--- a/02_DIA_inicio_2026_analisis_assets/rbd_9719_escuela-basica-santa-olga-de-kiev_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9719_escuela-basica-santa-olga-de-kiev_nt1_rubricas.xlsx
@@ -1800,13 +1800,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{519AEFD4-DB13-41CB-B751-034AED0040E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73D4BDF1-2A60-4082-B6A9-52C4CAB33658}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{270D92D0-A3BF-4CFA-A485-146452810DA2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC993450-3AEB-4C08-992C-054A642EE23B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58F85007-78D9-4B76-9C46-29DA87A95521}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9BB0605-C0FF-43AB-8F6C-AAFA65D3F6DD}"/>
 </file>